--- a/public/exports-with-coowners/29189668.xlsx
+++ b/public/exports-with-coowners/29189668.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215030</t>
+          <t xml:space="preserve">311215043</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -16189,7 +16189,7 @@
       </c>
       <c r="K216" t="inlineStr">
         <is>
-          <t xml:space="preserve">311393677</t>
+          <t xml:space="preserve">311393687</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
@@ -18289,7 +18289,7 @@
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407500</t>
+          <t xml:space="preserve">311407501</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
@@ -20539,7 +20539,7 @@
       </c>
       <c r="K274" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L274" t="inlineStr">
@@ -20614,7 +20614,7 @@
       </c>
       <c r="K275" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424644</t>
+          <t xml:space="preserve">311424656</t>
         </is>
       </c>
       <c r="L275" t="inlineStr">

--- a/public/exports-with-coowners/29189668.xlsx
+++ b/public/exports-with-coowners/29189668.xlsx
@@ -5464,7 +5464,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t xml:space="preserve">311215051</t>
+          <t xml:space="preserve">311215030</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -17764,7 +17764,7 @@
       </c>
       <c r="K237" t="inlineStr">
         <is>
-          <t xml:space="preserve">311407501</t>
+          <t xml:space="preserve">311407500</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">311424656</t>
+          <t xml:space="preserve">311424644</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="K327" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L327" t="inlineStr">
@@ -24589,7 +24589,7 @@
       </c>
       <c r="K328" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L328" t="inlineStr">
@@ -24664,7 +24664,7 @@
       </c>
       <c r="K329" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L329" t="inlineStr">
@@ -24739,7 +24739,7 @@
       </c>
       <c r="K330" t="inlineStr">
         <is>
-          <t xml:space="preserve">311929274</t>
+          <t xml:space="preserve">311929271</t>
         </is>
       </c>
       <c r="L330" t="inlineStr">
